--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785885</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131785740</v>
       </c>
       <c r="B4" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>131786116</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785885</v>
       </c>
       <c r="B2" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131785749</v>
       </c>
       <c r="B3" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131785740</v>
       </c>
       <c r="B4" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>131787318</v>
       </c>
       <c r="B5" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>131786116</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785885</v>
       </c>
       <c r="B2" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131785740</v>
       </c>
       <c r="B4" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>131786116</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131785885</v>
       </c>
       <c r="B2" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131785740</v>
       </c>
       <c r="B4" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131785885</v>
+        <v>131785740</v>
       </c>
       <c r="B2" t="n">
-        <v>58109</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528237</v>
+        <v>528195</v>
       </c>
       <c r="R2" t="n">
-        <v>6716202</v>
+        <v>6716194</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131785749</v>
+        <v>131786116</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,27 +802,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528198</v>
+        <v>528225</v>
       </c>
       <c r="R3" t="n">
-        <v>6716207</v>
+        <v>6716161</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,42 +903,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131785740</v>
+        <v>131785885</v>
       </c>
       <c r="B4" t="n">
-        <v>93180</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528195</v>
+        <v>528237</v>
       </c>
       <c r="R4" t="n">
-        <v>6716194</v>
+        <v>6716202</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131787318</v>
+        <v>131787332</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>58131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,27 +1026,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528229</v>
+        <v>528220</v>
       </c>
       <c r="R5" t="n">
-        <v>6716177</v>
+        <v>6716174</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,38 +1127,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131786116</v>
+        <v>131785749</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528225</v>
+        <v>528198</v>
       </c>
       <c r="R6" t="n">
-        <v>6716161</v>
+        <v>6716207</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1236,118 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131787318</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stugutjärnen, Stugutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528229</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6716177</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785740</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131786116</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785885</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131787332</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785749</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,8 +1378,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131787318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,50 +801,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131786116</v>
+        <v>136387951</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugutjärnen, Stugutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528225</v>
+        <v>528459</v>
       </c>
       <c r="R3" t="n">
-        <v>6716161</v>
+        <v>6716139</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,22 +866,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,44 +912,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131786116</t>
+          <t>https://artportalen.se/Sighting/136387951</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131785885</v>
+        <v>131786116</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528237</v>
+        <v>528225</v>
       </c>
       <c r="R4" t="n">
-        <v>6716202</v>
+        <v>6716161</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,38 +1029,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131785885</t>
+          <t>https://artportalen.se/Sighting/131786116</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131787332</v>
+        <v>131785885</v>
       </c>
       <c r="B5" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528220</v>
+        <v>528237</v>
       </c>
       <c r="R5" t="n">
-        <v>6716174</v>
+        <v>6716202</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,16 +1146,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131787332</t>
+          <t>https://artportalen.se/Sighting/131785885</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131785749</v>
+        <v>131787332</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>58131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,27 +1163,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528198</v>
+        <v>528220</v>
       </c>
       <c r="R6" t="n">
-        <v>6716207</v>
+        <v>6716174</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,13 +1263,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131785749</t>
+          <t>https://artportalen.se/Sighting/131787332</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131787318</v>
+        <v>131785749</v>
       </c>
       <c r="B7" t="n">
         <v>8460</v>
@@ -1300,7 +1300,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528229</v>
+        <v>528198</v>
       </c>
       <c r="R7" t="n">
-        <v>6716177</v>
+        <v>6716207</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,6 +1379,123 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131785749</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131787318</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stugutjärnen, Stugutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>528229</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6716177</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131787318</t>
         </is>
@@ -1392,6 +1509,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136387951</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 180-2026 artfynd.xlsx
+++ b/artfynd/A 180-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136387951</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
